--- a/bus-math-nextjs/public/resources/unit07-lesson06-teacher.xlsx
+++ b/bus-math-nextjs/public/resources/unit07-lesson06-teacher.xlsx
@@ -15,7 +15,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="SelectedScenario">'Inputs'!$B$4</definedName>
+    <definedName name="SelectedMethod">'Inputs'!$B$5</definedName>
+    <definedName name="SelectedKey">'Inputs'!$B$6</definedName>
+    <definedName name="UnitSellingPrice">'Inputs'!$B$8</definedName>
+    <definedName name="BeginningInventory">'Inputs'!$B$9</definedName>
+    <definedName name="GAFS">'Inputs'!$B$10</definedName>
+    <definedName name="SelectedUnitsSold">'Outputs'!$B$2</definedName>
+    <definedName name="SelectedCOGS">'Outputs'!$B$3</definedName>
+    <definedName name="SelectedEndingInventory">'Outputs'!$B$4</definedName>
+    <definedName name="Revenue">'KPI'!$B$2</definedName>
+    <definedName name="GrossMarginPct">'KPI'!$B$3</definedName>
+    <definedName name="AverageInventory">'KPI'!$B$4</definedName>
+    <definedName name="InventoryTurnover">'KPI'!$B$5</definedName>
+    <definedName name="DaysOnHand">'KPI'!$B$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -148,6 +163,34 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Drivers" displayName="Drivers" ref="A1:D4" headerRowCount="1">
+  <autoFilter ref="A1:D4"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Scenario"/>
+    <tableColumn id="2" name="UnitsSold"/>
+    <tableColumn id="3" name="DefaultMethod"/>
+    <tableColumn id="4" name="AsOfDate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MethodSummary" displayName="MethodSummary" ref="A1:F10" headerRowCount="1">
+  <autoFilter ref="A1:F10"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Key"/>
+    <tableColumn id="2" name="Scenario"/>
+    <tableColumn id="3" name="Method"/>
+    <tableColumn id="4" name="COGS"/>
+    <tableColumn id="5" name="EndingInventory"/>
+    <tableColumn id="6" name="BalanceCheck"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -512,7 +555,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>B4&amp;"|"&amp;B5</f>
+        <f>SelectedScenario&amp;"|"&amp;SelectedMethod</f>
         <v/>
       </c>
     </row>
@@ -547,6 +590,14 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Base,Stretch,Downside"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"FIFO,LIFO,Weighted Average"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -650,6 +701,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -725,7 +779,7 @@
         <v>460</v>
       </c>
       <c r="F2">
-        <f>D2+E2</f>
+        <f>[@COGS]+[@EndingInventory]</f>
         <v/>
       </c>
     </row>
@@ -752,7 +806,7 @@
         <v>380</v>
       </c>
       <c r="F3">
-        <f>D3+E3</f>
+        <f>[@COGS]+[@EndingInventory]</f>
         <v/>
       </c>
     </row>
@@ -779,7 +833,7 @@
         <v>418.18</v>
       </c>
       <c r="F4">
-        <f>D4+E4</f>
+        <f>[@COGS]+[@EndingInventory]</f>
         <v/>
       </c>
     </row>
@@ -806,7 +860,7 @@
         <v>372</v>
       </c>
       <c r="F5">
-        <f>D5+E5</f>
+        <f>[@COGS]+[@EndingInventory]</f>
         <v/>
       </c>
     </row>
@@ -833,7 +887,7 @@
         <v>300</v>
       </c>
       <c r="F6">
-        <f>D6+E6</f>
+        <f>[@COGS]+[@EndingInventory]</f>
         <v/>
       </c>
     </row>
@@ -860,7 +914,7 @@
         <v>334.55</v>
       </c>
       <c r="F7">
-        <f>D7+E7</f>
+        <f>[@COGS]+[@EndingInventory]</f>
         <v/>
       </c>
     </row>
@@ -887,7 +941,7 @@
         <v>526</v>
       </c>
       <c r="F8">
-        <f>D8+E8</f>
+        <f>[@COGS]+[@EndingInventory]</f>
         <v/>
       </c>
     </row>
@@ -914,7 +968,7 @@
         <v>440</v>
       </c>
       <c r="F9">
-        <f>D9+E9</f>
+        <f>[@COGS]+[@EndingInventory]</f>
         <v/>
       </c>
     </row>
@@ -941,12 +995,15 @@
         <v>480.91</v>
       </c>
       <c r="F10">
-        <f>D10+E10</f>
+        <f>[@COGS]+[@EndingInventory]</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -988,7 +1045,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>XLOOKUP(Inputs!$B$4,Drivers!$A$2:$A$4,Drivers!$B$2:$B$4)</f>
+        <f>XLOOKUP(SelectedScenario,Drivers[Scenario],Drivers[UnitsSold])</f>
         <v/>
       </c>
       <c r="C2" t="inlineStr">
@@ -1004,7 +1061,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>XLOOKUP(Inputs!$B$6,MethodSummary!$A$2:$A$10,MethodSummary!$D$2:$D$10)</f>
+        <f>XLOOKUP(SelectedKey,MethodSummary[Key],MethodSummary[COGS])</f>
         <v/>
       </c>
       <c r="C3" t="inlineStr">
@@ -1020,7 +1077,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>XLOOKUP(Inputs!$B$6,MethodSummary!$A$2:$A$10,MethodSummary!$E$2:$E$10)</f>
+        <f>XLOOKUP(SelectedKey,MethodSummary[Key],MethodSummary[EndingInventory])</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
@@ -1036,7 +1093,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>Inputs!$B$10</f>
+        <f>GAFS</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
@@ -1088,7 +1145,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>Outputs!$B$2*Inputs!$B$8</f>
+        <f>SelectedUnitsSold*UnitSellingPrice</f>
         <v/>
       </c>
       <c r="C2" t="inlineStr">
@@ -1104,7 +1161,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>(B2-Outputs!$B$3)/B2</f>
+        <f>(Revenue-SelectedCOGS)/Revenue</f>
         <v/>
       </c>
       <c r="C3" t="inlineStr">
@@ -1120,7 +1177,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>(Inputs!$B$9+Outputs!$B$4)/2</f>
+        <f>(BeginningInventory+SelectedEndingInventory)/2</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
@@ -1136,7 +1193,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>Outputs!$B$3/B4</f>
+        <f>SelectedCOGS/AverageInventory</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
@@ -1152,7 +1209,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>365/B5</f>
+        <f>365/InventoryTurnover</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
@@ -1204,12 +1261,12 @@
         </is>
       </c>
       <c r="B2">
-        <f>IF(ABS((Outputs!$B$3+Outputs!$B$4)-Outputs!$B$5)&lt;0.01,"Balanced","Check")</f>
+        <f>IF(ABS((SelectedCOGS+SelectedEndingInventory)-GAFS)&lt;0.01,"Balanced","Check")</f>
         <v/>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IF(ABS((SelectedCOGS+SelectedEI)-GAFS)&lt;0.01,"Balanced","Check")</t>
+          <t>IF(ABS((SelectedCOGS+SelectedEndingInventory)-GAFS)&lt;0.01,"Balanced","Check")</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1277,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>IFNA(XLOOKUP(Inputs!$B$6,MethodSummary!$A$2:$A$10,MethodSummary!$D$2:$D$10),"Missing Key")</f>
+        <f>IFNA(XLOOKUP(SelectedKey,MethodSummary[Key],MethodSummary[COGS]),"Missing Key")</f>
         <v/>
       </c>
       <c r="C3" t="inlineStr">
@@ -1236,7 +1293,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>IF(Outputs!$B$2&gt;0,"OK","Check Drivers")</f>
+        <f>IF(SelectedUnitsSold&gt;0,"OK","Check Drivers")</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
@@ -1288,7 +1345,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>Inputs!$B$4</f>
+        <f>SelectedScenario</f>
         <v/>
       </c>
       <c r="C2" t="inlineStr">
@@ -1304,7 +1361,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>Inputs!$B$5</f>
+        <f>SelectedMethod</f>
         <v/>
       </c>
       <c r="C3" t="inlineStr">
@@ -1320,7 +1377,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>Outputs!$B$3</f>
+        <f>SelectedCOGS</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
@@ -1336,7 +1393,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>Outputs!$B$4</f>
+        <f>SelectedEndingInventory</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
@@ -1352,7 +1409,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>KPI!$B$5</f>
+        <f>InventoryTurnover</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
@@ -1368,7 +1425,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>KPI!$B$6</f>
+        <f>DaysOnHand</f>
         <v/>
       </c>
       <c r="C7" t="inlineStr">
@@ -1384,7 +1441,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>KPI!$B$3</f>
+        <f>GrossMarginPct</f>
         <v/>
       </c>
       <c r="C8" t="inlineStr">
